--- a/Luban/MiniTemplate/Datas/#Skill.xlsx
+++ b/Luban/MiniTemplate/Datas/#Skill.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unityRes\sourceCode\XHSkill\HFSkillFramework\Luban\MiniTemplate\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16140" windowHeight="9864"/>
+    <workbookView windowWidth="28800" windowHeight="13455"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,13 +79,13 @@
     <t>战士技能</t>
   </si>
   <si>
-    <t>横扫</t>
-  </si>
-  <si>
-    <t>ScriptObject\SkillAsset\横扫</t>
-  </si>
-  <si>
-    <t>Sprites/SkillIcon/01101</t>
+    <t>横扫2</t>
+  </si>
+  <si>
+    <t>ScriptObject\SkillAsset\MySkillAsset\横扫2</t>
+  </si>
+  <si>
+    <t>Sprites/SkillIcon/00341</t>
   </si>
   <si>
     <t>流血</t>
@@ -1116,16 +1121,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="17.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="16.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="42.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="44.7777777777778" customWidth="1"/>
+    <col min="3" max="3" width="17.8916666666667" customWidth="1"/>
+    <col min="4" max="4" width="16.225" customWidth="1"/>
+    <col min="5" max="5" width="42.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="44.775" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="16.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="16.8916666666667" customWidth="1"/>
     <col min="9" max="9" width="14.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="22.5555555555556" customWidth="1"/>
+    <col min="10" max="10" width="22.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
